--- a/datos/oportunidades_financiacion.xlsx
+++ b/datos/oportunidades_financiacion.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wramirez\OneDrive\UNPHU\Fuentes Financiacion Externas 2026\web\portal_financiamiento_github\datos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wramirez\OneDrive\UNPHU\Fuentes Financiacion Externas 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{1C8BC400-E995-42A4-AD2F-852A6B3ABAD0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{4CAF48B7-30E7-44F1-9225-C2FE8CCE66C7}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{1C8BC400-E995-42A4-AD2F-852A6B3ABAD0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{0F0C9F12-A666-4DF3-BD4A-93AE0CB7FE66}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3341" uniqueCount="1808">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3433" uniqueCount="1860">
   <si>
     <t>ID</t>
   </si>
@@ -5457,6 +5457,162 @@
   </si>
   <si>
     <t>Elegible y abierta. Para maximizar encaje con brecha digital, conviene reformular hacia una pregunta causal vinculada con gobierno digital, regulación o conectividad y sus efectos diferenciados sobre oportunidades económicas.</t>
+  </si>
+  <si>
+    <t>Research and Higher Education Technology Fund</t>
+  </si>
+  <si>
+    <t>NLnet Foundation / Vietsch Foundation</t>
+  </si>
+  <si>
+    <t>Países Bajos</t>
+  </si>
+  <si>
+    <t>Investigador; profesor; desarrollador de tecnología abierta</t>
+  </si>
+  <si>
+    <t>Institución académica; institución de investigación; persona individual; ONG; empresa</t>
+  </si>
+  <si>
+    <t>Tecnologías de Internet; investigación y educación superior</t>
+  </si>
+  <si>
+    <t>Internet abierto; resiliencia; tecnología abierta; investigación; educación superior; redes; software libre; datos abiertos</t>
+  </si>
+  <si>
+    <t>Fondo de NLnet y Vietsch Foundation para pequeñas iniciativas de investigación y educación superior que contribuyan al futuro de Internet y generen resultados tecnológicos o científicos abiertos.</t>
+  </si>
+  <si>
+    <t>INTEC/PUCMM y sus investigadores pueden ser elegibles. NLnet admite en principio individuos, organizaciones de investigación, organizaciones sin fines de lucro, instituciones públicas y empresas; deben cumplirse las condiciones específicas del fondo.</t>
+  </si>
+  <si>
+    <t>Convocatoria abierta con cortes periódicos. Próximo deadline: 03/11/2026 a las 12:00 CET. Primer grant entre EUR 5,000 y 50,000. Los resultados científicos deben publicarse en acceso abierto y el software/hardware desarrollado bajo licencias libres y de código abierto.</t>
+  </si>
+  <si>
+    <t>https://nlnet.nl/nren/</t>
+  </si>
+  <si>
+    <t>NLnet Foundation / Vietsch Foundation — Research and Higher Education Technology Fund</t>
+  </si>
+  <si>
+    <t>Prioridad alta para brecha digital si la propuesta produce una metodología, dataset, software o herramienta abierta para medir desigualdad, resiliencia o desarrollo territorial de Internet.</t>
+  </si>
+  <si>
+    <t>ICANN Grant Program</t>
+  </si>
+  <si>
+    <t>Internet Corporation for Assigned Names and Numbers (ICANN)</t>
+  </si>
+  <si>
+    <t>Investigadores; equipos técnicos; organizaciones sin fines de lucro</t>
+  </si>
+  <si>
+    <t>Organización benéfica; ONG; institución académica sin fines de lucro elegible</t>
+  </si>
+  <si>
+    <t>Infraestructura de Internet; DNS; identificadores únicos; seguridad y resiliencia</t>
+  </si>
+  <si>
+    <t>DNS; DNSSEC; IPv6; seguridad; resiliencia; identificadores únicos; Internet; estándares abiertos</t>
+  </si>
+  <si>
+    <t>Programa global de ICANN financiado con ingresos de subastas de nuevos gTLD para proyectos alineados con su misión de asegurar la operación estable y segura de los sistemas de identificadores únicos de Internet.</t>
+  </si>
+  <si>
+    <t>INTEC/PUCMM podrían ser elegibles institucionalmente si acreditan naturaleza benéfica equivalente a una organización estadounidense 501(c)(3), cumplen la debida diligencia y pueden recibir transferencias desde una institución financiera de Estados Unidos.</t>
+  </si>
+  <si>
+    <t>El primer ciclo está cerrado y, al 08/09/2026, ICANN no ha publicado la fecha de apertura del siguiente ciclo. Los montos de USD 50,000-500,000 y duración máxima de 24 meses corresponden al primer ciclo y pueden ser revisados en ciclos futuros.</t>
+  </si>
+  <si>
+    <t>https://www.icann.org/en/grant-program</t>
+  </si>
+  <si>
+    <t>ICANN — ICANN Grant Program</t>
+  </si>
+  <si>
+    <t>Prioridad media-alta para líneas sobre DNS, DNSSEC, IPv6, resiliencia e infraestructura de Internet. Encaje menor para una propuesta centrada únicamente en penetración o brecha digital de acceso.</t>
+  </si>
+  <si>
+    <t>Internet Freedom Fund</t>
+  </si>
+  <si>
+    <t>Open Technology Fund (OTF)</t>
+  </si>
+  <si>
+    <t>Hasta 24 meses; rango ideal 6-12 meses</t>
+  </si>
+  <si>
+    <t>Investigadores; desarrolladores; organizaciones de sociedad civil; expertos en seguridad digital</t>
+  </si>
+  <si>
+    <t>Persona individual; ONG; institución académica; empresa</t>
+  </si>
+  <si>
+    <t>Libertad de Internet; ciberseguridad; censura y vigilancia</t>
+  </si>
+  <si>
+    <t>Internet freedom; censura; vigilancia; seguridad digital; privacidad; medición de Internet; investigación aplicada; tecnologías abiertas</t>
+  </si>
+  <si>
+    <t>Fondo principal de OTF para proyectos innovadores de libertad de Internet. Financia desarrollo tecnológico, investigación aplicada, seguridad digital y encuentros orientados a combatir censura, vigilancia y amenazas al acceso seguro y abierto a Internet.</t>
+  </si>
+  <si>
+    <t>Pueden aplicar individuos y organizaciones con o sin fines de lucro dentro o fuera de Estados Unidos. La propuesta debe encajar directamente con la misión de libertad de Internet y beneficiar a usuarios en entornos afectados por censura, vigilancia o restricciones.</t>
+  </si>
+  <si>
+    <t>Concept notes aceptadas de forma continua y revisadas mensualmente. Monto permitido: USD 10,000-900,000; rango ideal USD 50,000-200,000 por 6-12 meses. OTF opera mediante contratos, no grants tradicionales. No financia proyectos generales de conectividad o ICT4D.</t>
+  </si>
+  <si>
+    <t>https://www.opentech.fund/funds/internet-freedom-fund/</t>
+  </si>
+  <si>
+    <t>Open Technology Fund — Internet Freedom Fund</t>
+  </si>
+  <si>
+    <t>Encaje limitado con brecha digital de acceso. Puede ser relevante si la investigación se reorienta a seguridad digital, censura, vigilancia, medición de interferencias o resiliencia de comunidades expuestas a restricciones de Internet.</t>
+  </si>
+  <si>
+    <t>Heilbronn AI Fellowships</t>
+  </si>
+  <si>
+    <t>DAAD (German Academic Exchange Service) / Dieter Schwarz Stiftung</t>
+  </si>
+  <si>
+    <t>1–12 meses</t>
+  </si>
+  <si>
+    <t>Investigador emergente; Postdoctorado</t>
+  </si>
+  <si>
+    <t>Internacional; estancia de investigación en Heilbronn, Alemania</t>
+  </si>
+  <si>
+    <t>Sin restricción general; solicitantes internacionales</t>
+  </si>
+  <si>
+    <t>Inteligencia Artificial</t>
+  </si>
+  <si>
+    <t>IA; inteligencia artificial; investigación; posdoctorado; movilidad internacional; Heilbronn; innovación</t>
+  </si>
+  <si>
+    <t>Programa internacional de estancias de investigación para doctorandos en fase final y jóvenes investigadores posdoctorales que trabajen en inteligencia artificial, ya sea como campo principal o como herramienta aplicada a otras disciplinas. La estancia se realiza en una institución anfitriona participante en Heilbronn, Alemania.</t>
+  </si>
+  <si>
+    <t>Pueden aplicar doctorandos internacionales en la fase final del doctorado y jóvenes investigadores cuyo doctorado haya sido obtenido hace no más de 5 años. Se requiere afiliación a una universidad o institución de investigación, muy buen nivel de inglés, residencia fuera de Alemania durante los 15 meses previos a la solicitud y un proyecto preparado conjuntamente con un investigador anfitrión de una institución participante en Heilbronn.</t>
+  </si>
+  <si>
+    <t>Convocatoria continua. La solicitud debe presentarse al menos cuatro meses antes de la fecha prevista de inicio. La estancia puede durar de 1 a 12 meses. El estipendio es de EUR 2,800 mensuales, con apoyo adicional para seguro y viaje internacional según las condiciones del programa. El monto máximo registrado corresponde a 12 meses de estipendio (EUR 33,600), sin incluir beneficios adicionales.</t>
+  </si>
+  <si>
+    <t>https://www2.daad.de/deutschland/stipendium/datenbank/en/21148-scholarship-database/?origin=54&amp;status=4&amp;subjectGrps=&amp;daad=&amp;q=heilbronn&amp;page=1&amp;detail=57883183#voraussetzungen</t>
+  </si>
+  <si>
+    <t>DAAD — Heilbronn AI Fellowships</t>
+  </si>
+  <si>
+    <t>Aplicable a investigadores de UNPHU que cumplan el perfil individual. Requiere identificar un anfitrión en una institución participante de Heilbronn y preparar conjuntamente la propuesta. Especialmente relevante para investigadores jóvenes que utilicen IA como campo de investigación o como herramienta aplicada.</t>
   </si>
 </sst>
 </file>
@@ -15612,7 +15768,7 @@
         <v>1587</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>1263</v>
+        <v>54</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>1509</v>
@@ -17780,157 +17936,367 @@
         <v>1807</v>
       </c>
     </row>
-    <row r="134" spans="1:30">
+    <row r="134" spans="1:30" ht="99.75">
       <c r="A134" s="4" t="str">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="B134" s="4"/>
-      <c r="C134" s="4"/>
-      <c r="D134" s="4"/>
-      <c r="E134" s="4"/>
-      <c r="F134" s="4"/>
-      <c r="G134" s="6"/>
-      <c r="H134" s="4"/>
-      <c r="I134" s="4"/>
-      <c r="J134" s="4"/>
+        <v>OP-0133</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>1808</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>1809</v>
+      </c>
+      <c r="E134" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F134" s="4" t="s">
+        <v>1810</v>
+      </c>
+      <c r="G134" s="6">
+        <v>46329</v>
+      </c>
+      <c r="H134" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I134" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J134" s="4" t="s">
+        <v>38</v>
+      </c>
       <c r="K134" s="4" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>Sin fecha</v>
-      </c>
-      <c r="L134" s="8"/>
-      <c r="M134" s="8"/>
-      <c r="N134" s="4"/>
-      <c r="O134" s="4"/>
-      <c r="P134" s="4"/>
-      <c r="Q134" s="4"/>
-      <c r="R134" s="4"/>
-      <c r="S134" s="4"/>
-      <c r="T134" s="4"/>
-      <c r="U134" s="4"/>
-      <c r="V134" s="4"/>
-      <c r="W134" s="4"/>
-      <c r="X134" s="4"/>
-      <c r="Y134" s="4"/>
-      <c r="Z134" s="4"/>
+        <v>Abierta</v>
+      </c>
+      <c r="L134" s="8">
+        <v>5000</v>
+      </c>
+      <c r="M134" s="8">
+        <v>50000</v>
+      </c>
+      <c r="N134" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="O134" s="4" t="s">
+        <v>1077</v>
+      </c>
+      <c r="P134" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q134" s="4" t="s">
+        <v>1811</v>
+      </c>
+      <c r="R134" s="4" t="s">
+        <v>1812</v>
+      </c>
+      <c r="S134" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="T134" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="U134" s="4" t="s">
+        <v>1813</v>
+      </c>
+      <c r="V134" s="4" t="s">
+        <v>1814</v>
+      </c>
+      <c r="W134" s="4" t="s">
+        <v>1815</v>
+      </c>
+      <c r="X134" s="4" t="s">
+        <v>1816</v>
+      </c>
+      <c r="Y134" s="4" t="s">
+        <v>1817</v>
+      </c>
+      <c r="Z134" s="4" t="s">
+        <v>1818</v>
+      </c>
       <c r="AA134" s="4"/>
-      <c r="AB134" s="6"/>
-      <c r="AC134" s="4"/>
-      <c r="AD134" s="4"/>
-    </row>
-    <row r="135" spans="1:30">
+      <c r="AB134" s="6">
+        <v>46273</v>
+      </c>
+      <c r="AC134" s="4" t="s">
+        <v>1819</v>
+      </c>
+      <c r="AD134" s="4" t="s">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="135" spans="1:30" ht="99.75">
       <c r="A135" s="4" t="str">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="B135" s="4"/>
-      <c r="C135" s="4"/>
-      <c r="D135" s="4"/>
-      <c r="E135" s="4"/>
-      <c r="F135" s="4"/>
+        <v>OP-0134</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>1821</v>
+      </c>
+      <c r="D135" s="4" t="s">
+        <v>1822</v>
+      </c>
+      <c r="E135" s="4" t="s">
+        <v>1266</v>
+      </c>
+      <c r="F135" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="G135" s="6"/>
-      <c r="H135" s="4"/>
-      <c r="I135" s="4"/>
-      <c r="J135" s="4"/>
+      <c r="H135" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="I135" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="J135" s="4" t="s">
+        <v>88</v>
+      </c>
       <c r="K135" s="4" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>Sin fecha</v>
-      </c>
-      <c r="L135" s="8"/>
-      <c r="M135" s="8"/>
-      <c r="N135" s="4"/>
-      <c r="O135" s="4"/>
-      <c r="P135" s="4"/>
-      <c r="Q135" s="4"/>
-      <c r="R135" s="4"/>
-      <c r="S135" s="4"/>
-      <c r="T135" s="4"/>
-      <c r="U135" s="4"/>
-      <c r="V135" s="4"/>
-      <c r="W135" s="4"/>
-      <c r="X135" s="4"/>
-      <c r="Y135" s="4"/>
-      <c r="Z135" s="4"/>
+        <v>Cerrada</v>
+      </c>
+      <c r="L135" s="8">
+        <v>50000</v>
+      </c>
+      <c r="M135" s="8">
+        <v>500000</v>
+      </c>
+      <c r="N135" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O135" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="P135" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q135" s="4" t="s">
+        <v>1823</v>
+      </c>
+      <c r="R135" s="4" t="s">
+        <v>1824</v>
+      </c>
+      <c r="S135" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="T135" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="U135" s="4" t="s">
+        <v>1825</v>
+      </c>
+      <c r="V135" s="4" t="s">
+        <v>1826</v>
+      </c>
+      <c r="W135" s="4" t="s">
+        <v>1827</v>
+      </c>
+      <c r="X135" s="4" t="s">
+        <v>1828</v>
+      </c>
+      <c r="Y135" s="4" t="s">
+        <v>1829</v>
+      </c>
+      <c r="Z135" s="4" t="s">
+        <v>1830</v>
+      </c>
       <c r="AA135" s="4"/>
-      <c r="AB135" s="6"/>
-      <c r="AC135" s="4"/>
-      <c r="AD135" s="4"/>
-    </row>
-    <row r="136" spans="1:30">
+      <c r="AB135" s="6">
+        <v>46273</v>
+      </c>
+      <c r="AC135" s="4" t="s">
+        <v>1831</v>
+      </c>
+      <c r="AD135" s="4" t="s">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="136" spans="1:30" ht="99.75">
       <c r="A136" s="4" t="str">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="B136" s="4"/>
-      <c r="C136" s="4"/>
-      <c r="D136" s="4"/>
-      <c r="E136" s="4"/>
-      <c r="F136" s="4"/>
+        <v>OP-0135</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D136" s="4" t="s">
+        <v>1834</v>
+      </c>
+      <c r="E136" s="4" t="s">
+        <v>1266</v>
+      </c>
+      <c r="F136" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="G136" s="6"/>
-      <c r="H136" s="4"/>
-      <c r="I136" s="4"/>
-      <c r="J136" s="4"/>
+      <c r="H136" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I136" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J136" s="4" t="s">
+        <v>38</v>
+      </c>
       <c r="K136" s="4" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>Sin fecha</v>
       </c>
-      <c r="L136" s="8"/>
-      <c r="M136" s="8"/>
-      <c r="N136" s="4"/>
-      <c r="O136" s="4"/>
-      <c r="P136" s="4"/>
-      <c r="Q136" s="4"/>
-      <c r="R136" s="4"/>
-      <c r="S136" s="4"/>
-      <c r="T136" s="4"/>
-      <c r="U136" s="4"/>
-      <c r="V136" s="4"/>
-      <c r="W136" s="4"/>
-      <c r="X136" s="4"/>
-      <c r="Y136" s="4"/>
-      <c r="Z136" s="4"/>
+      <c r="L136" s="8">
+        <v>10000</v>
+      </c>
+      <c r="M136" s="8">
+        <v>900000</v>
+      </c>
+      <c r="N136" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O136" s="4" t="s">
+        <v>1835</v>
+      </c>
+      <c r="P136" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q136" s="4" t="s">
+        <v>1836</v>
+      </c>
+      <c r="R136" s="4" t="s">
+        <v>1837</v>
+      </c>
+      <c r="S136" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="T136" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="U136" s="4" t="s">
+        <v>1838</v>
+      </c>
+      <c r="V136" s="4" t="s">
+        <v>1839</v>
+      </c>
+      <c r="W136" s="4" t="s">
+        <v>1840</v>
+      </c>
+      <c r="X136" s="4" t="s">
+        <v>1841</v>
+      </c>
+      <c r="Y136" s="4" t="s">
+        <v>1842</v>
+      </c>
+      <c r="Z136" s="4" t="s">
+        <v>1843</v>
+      </c>
       <c r="AA136" s="4"/>
-      <c r="AB136" s="6"/>
-      <c r="AC136" s="4"/>
-      <c r="AD136" s="4"/>
+      <c r="AB136" s="6">
+        <v>46273</v>
+      </c>
+      <c r="AC136" s="4" t="s">
+        <v>1844</v>
+      </c>
+      <c r="AD136" s="4" t="s">
+        <v>1845</v>
+      </c>
     </row>
     <row r="137" spans="1:30">
       <c r="A137" s="4" t="str">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="B137" s="4"/>
-      <c r="C137" s="4"/>
-      <c r="D137" s="4"/>
-      <c r="E137" s="4"/>
-      <c r="F137" s="4"/>
+        <v>OP-0136</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>1846</v>
+      </c>
+      <c r="D137" s="4" t="s">
+        <v>1847</v>
+      </c>
+      <c r="E137" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F137" s="4" t="s">
+        <v>906</v>
+      </c>
       <c r="G137" s="6"/>
-      <c r="H137" s="4"/>
-      <c r="I137" s="4"/>
-      <c r="J137" s="4"/>
+      <c r="H137" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I137" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J137" s="4" t="s">
+        <v>38</v>
+      </c>
       <c r="K137" s="4" t="str">
         <f t="shared" ca="1" si="5"/>
         <v>Sin fecha</v>
       </c>
-      <c r="L137" s="8"/>
-      <c r="M137" s="8"/>
-      <c r="N137" s="4"/>
-      <c r="O137" s="4"/>
-      <c r="P137" s="4"/>
-      <c r="Q137" s="4"/>
-      <c r="R137" s="4"/>
-      <c r="S137" s="4"/>
-      <c r="T137" s="4"/>
-      <c r="U137" s="4"/>
-      <c r="V137" s="4"/>
-      <c r="W137" s="4"/>
-      <c r="X137" s="4"/>
-      <c r="Y137" s="4"/>
-      <c r="Z137" s="4"/>
+      <c r="L137" s="8">
+        <v>2800</v>
+      </c>
+      <c r="M137" s="8">
+        <v>33600</v>
+      </c>
+      <c r="N137" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="O137" s="4" t="s">
+        <v>1848</v>
+      </c>
+      <c r="P137" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q137" s="4" t="s">
+        <v>1849</v>
+      </c>
+      <c r="R137" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="S137" s="4" t="s">
+        <v>1850</v>
+      </c>
+      <c r="T137" s="4" t="s">
+        <v>1851</v>
+      </c>
+      <c r="U137" s="4" t="s">
+        <v>1852</v>
+      </c>
+      <c r="V137" s="4" t="s">
+        <v>1853</v>
+      </c>
+      <c r="W137" s="4" t="s">
+        <v>1854</v>
+      </c>
+      <c r="X137" s="4" t="s">
+        <v>1855</v>
+      </c>
+      <c r="Y137" s="4" t="s">
+        <v>1856</v>
+      </c>
+      <c r="Z137" s="4" t="s">
+        <v>1857</v>
+      </c>
       <c r="AA137" s="4"/>
-      <c r="AB137" s="6"/>
-      <c r="AC137" s="4"/>
-      <c r="AD137" s="4"/>
+      <c r="AB137" s="6">
+        <v>46283</v>
+      </c>
+      <c r="AC137" s="4" t="s">
+        <v>1858</v>
+      </c>
+      <c r="AD137" s="4" t="s">
+        <v>1859</v>
+      </c>
     </row>
     <row r="138" spans="1:30">
       <c r="A138" s="4" t="str">

--- a/datos/oportunidades_financiacion.xlsx
+++ b/datos/oportunidades_financiacion.xlsx
@@ -18298,43 +18298,143 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="138" spans="1:30">
+    <row r="138" spans="1:30" ht="252" customHeight="1">
       <c r="A138" s="4" t="str">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="B138" s="4"/>
-      <c r="C138" s="4"/>
-      <c r="D138" s="4"/>
-      <c r="E138" s="4"/>
-      <c r="F138" s="4"/>
-      <c r="G138" s="6"/>
-      <c r="H138" s="4"/>
-      <c r="I138" s="4"/>
-      <c r="J138" s="4"/>
+        <v>OP-0137</v>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sí</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOSTER &amp; Science Microbiome Prize 2027</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOSTER Inc. / Science–AAAS</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Empresa privada</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Internacional</t>
+        </is>
+      </c>
+      <c r="G138" s="6">
+        <v>46432</v>
+      </c>
+      <c r="H138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirmada</t>
+        </is>
+      </c>
+      <c r="I138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solicitud</t>
+        </is>
+      </c>
+      <c r="J138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abierta</t>
+        </is>
+      </c>
       <c r="K138" s="4" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>Sin fecha</v>
-      </c>
-      <c r="L138" s="8"/>
-      <c r="M138" s="8"/>
-      <c r="N138" s="4"/>
-      <c r="O138" s="4"/>
-      <c r="P138" s="4"/>
-      <c r="Q138" s="4"/>
-      <c r="R138" s="4"/>
-      <c r="S138" s="4"/>
-      <c r="T138" s="4"/>
-      <c r="U138" s="4"/>
-      <c r="V138" s="4"/>
-      <c r="W138" s="4"/>
-      <c r="X138" s="4"/>
-      <c r="Y138" s="4"/>
-      <c r="Z138" s="4"/>
+        <v>Abierta</v>
+      </c>
+      <c r="L138" s="8">
+        <v>25000</v>
+      </c>
+      <c r="M138" s="8">
+        <v>25000</v>
+      </c>
+      <c r="N138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD</t>
+        </is>
+      </c>
+      <c r="O138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No aplica (premio)</t>
+        </is>
+      </c>
+      <c r="P138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Premio</t>
+        </is>
+      </c>
+      <c r="Q138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Investigador emergente</t>
+        </is>
+      </c>
+      <c r="R138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Persona individual</t>
+        </is>
+      </c>
+      <c r="S138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Internacional</t>
+        </is>
+      </c>
+      <c r="T138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sin restricción</t>
+        </is>
+      </c>
+      <c r="U138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Microbioma; salud humana y veterinaria</t>
+        </is>
+      </c>
+      <c r="V138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Microbiota; microbioma; funciones microbianas; salud; enfermedad; intervenciones terapéuticas; investigadores emergentes</t>
+        </is>
+      </c>
+      <c r="W138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Premio internacional a investigaciones innovadoras sobre funciones de la microbiota de cualquier organismo, con potencial para comprender la salud y las enfermedades humanas o veterinarias o guiar terapias. El ganador recibe USD 25,000 y publica su ensayo en Science, en papel y en línea.</t>
+        </is>
+      </c>
+      <c r="X138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Científicos en etapas iniciales con M.D., Ph.D. o M.D./Ph.D. obtenido en los últimos 10 años. Postulación individual centrada en la contribución propia; el candidato debe haber realizado o dirigido el trabajo en los últimos 3 años. Se exige al menos una publicación de investigación revisada por pares en los 3 años calendario anteriores. La segunda publicación es opcional y puede ser un preprint enviado. No se admiten revisiones ni comentarios. Hay extensiones de elegibilidad por maternidad y licencias justificadas.</t>
+        </is>
+      </c>
+      <c r="Y138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cierre: 14/02/2027, 23:59, hora del este indicada en las bases. Sin tasa de inscripción. Presentar formulario, ensayo propio en Word de hasta 1,000 palabras, CV, carta de recomendación de una página y 1–2 publicaciones. Se permite una figura o tabla y hasta 15 referencias, excluidas del límite de palabras. Se evalúan calidad y relevancia científica y claridad de escritura. No se permite generar el ensayo ni sus figuras con IA; la edición limitada con Grammarly debe declararse. Hasta dos finalistas publican en línea. El premio contempla viaje y alojamiento razonables para la ceremonia, si procede.</t>
+        </is>
+      </c>
+      <c r="Z138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.science.org/content/prize-award/noster-and-science-microbiome-prize</t>
+        </is>
+      </c>
       <c r="AA138" s="4"/>
-      <c r="AB138" s="6"/>
-      <c r="AC138" s="4"/>
-      <c r="AD138" s="4"/>
+      <c r="AB138" s="6">
+        <v>46315</v>
+      </c>
+      <c r="AC138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Science/AAAS — NOSTER 2027. Bases: https://noster.secure-platform.com/a/page/Rules</t>
+        </is>
+      </c>
+      <c r="AD138" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patrocinio: NOSTER Inc. (Japón); organización: Science/AAAS (Estados Unidos). Premio a resultados ya obtenidos. La sección III.1 de las reglas menciona IA, en discrepancia con el alcance y la página de elegibilidad sobre microbioma. Confirmar con NosterSciencePrize@aaas.org.</t>
+        </is>
+      </c>
     </row>
     <row r="139" spans="1:30">
       <c r="A139" s="4" t="str">
